--- a/artfynd/A 64289-2021 artfynd.xlsx
+++ b/artfynd/A 64289-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64289-2021 artfynd.xlsx
+++ b/artfynd/A 64289-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100078720</v>
+        <v>102334403</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2387</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granön, Nb</t>
+          <t>Kalix, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>892140.59230468</v>
+        <v>891621</v>
       </c>
       <c r="R2" t="n">
-        <v>7315543.811931515</v>
+        <v>7315984</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,67 +766,59 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maria Stoltz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maria Stoltz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100078705</v>
+        <v>100078713</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>891870.0593047945</v>
+        <v>891337</v>
       </c>
       <c r="R3" t="n">
-        <v>7315662.380057276</v>
+        <v>7315865</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,19 +861,9 @@
           <t>2022-04-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,19 +890,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100078718</v>
+        <v>110311519</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -957,7 +923,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -967,13 +933,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>892064.5008710007</v>
+        <v>891362</v>
       </c>
       <c r="R4" t="n">
-        <v>7315408.872080766</v>
+        <v>7315801</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,49 +983,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maria Stoltz</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Maria Stoltz</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100078722</v>
+        <v>100078703</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1077,7 +1028,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1087,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>892131.3477766616</v>
+        <v>891314</v>
       </c>
       <c r="R5" t="n">
-        <v>7315498.82523889</v>
+        <v>7315912</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1120,19 +1071,9 @@
           <t>2022-04-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,53 +1100,44 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100078725</v>
+        <v>100078705</v>
       </c>
       <c r="B6" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1215,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>891892.9782472391</v>
+        <v>891870</v>
       </c>
       <c r="R6" t="n">
-        <v>7315677.599053372</v>
+        <v>7315662</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,19 +1180,9 @@
           <t>2022-04-13</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,32 +1209,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100078721</v>
+        <v>100078725</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103042</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1320,12 +1237,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1335,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>892145.1218588152</v>
+        <v>891893</v>
       </c>
       <c r="R7" t="n">
-        <v>7315507.794911167</v>
+        <v>7315678</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1368,19 +1293,9 @@
           <t>2022-04-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,19 +1322,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100078713</v>
+        <v>100078715</v>
       </c>
       <c r="B8" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1445,20 +1355,20 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granön, Nb</t>
+          <t>g, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>891337.5114170944</v>
+        <v>891937</v>
       </c>
       <c r="R8" t="n">
-        <v>7315865.340614381</v>
+        <v>7315518</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1488,19 +1398,9 @@
           <t>2022-04-13</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-04-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,19 +1427,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110311519</v>
+        <v>100078717</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1565,7 +1460,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1575,13 +1470,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>891362.1852933455</v>
+        <v>891942</v>
       </c>
       <c r="R9" t="n">
-        <v>7315800.869760725</v>
+        <v>7315479</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1605,22 +1500,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,15 +1520,435 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Maria Stoltz</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Maria Stoltz</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100078718</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Granön, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>892065</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7315409</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100078720</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Granön, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>892141</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7315544</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100078721</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Granön, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>892145</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7315508</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100078722</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Granön, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>892130</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7315499</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-04-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
